--- a/Activity_01/Day08_Pivots_LuckyRomanceGilhang.xlsx
+++ b/Activity_01/Day08_Pivots_LuckyRomanceGilhang.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Day09_HR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Day09_HR\Day8_Introduction_to_Data_Summarization_&amp;_Pivot_Tables\Activity_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33CCBA93-2D0F-4D13-AB8A-4CAB232530AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E9BC61-58BB-4654-A369-33EF06A7EE77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="4" r:id="rId1"/>
@@ -18,19 +18,20 @@
     <sheet name="Table 3" sheetId="7" r:id="rId3"/>
     <sheet name="Table 4" sheetId="8" r:id="rId4"/>
     <sheet name="Table 5" sheetId="11" r:id="rId5"/>
-    <sheet name="Hire_Date_summary" sheetId="5" r:id="rId6"/>
-    <sheet name="Employees" sheetId="1" r:id="rId7"/>
-    <sheet name="Instructions" sheetId="2" r:id="rId8"/>
+    <sheet name="journal #8" sheetId="13" r:id="rId6"/>
+    <sheet name="Hire_Date_summary" sheetId="5" r:id="rId7"/>
+    <sheet name="Employees" sheetId="1" r:id="rId8"/>
+    <sheet name="Instructions" sheetId="2" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId9"/>
+    <pivotCache cacheId="2" r:id="rId10"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="159">
   <si>
     <t>employee_id</t>
   </si>
@@ -518,7 +519,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -631,7 +632,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -650,30 +651,31 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -805,7 +807,57 @@
       <fieldGroup par="10"/>
     </cacheField>
     <cacheField name="salary" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="26100" maxValue="85000"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="26100" maxValue="85000" count="49">
+        <n v="28500"/>
+        <n v="65000"/>
+        <n v="26300"/>
+        <n v="38200"/>
+        <n v="27750"/>
+        <n v="39760"/>
+        <n v="27000"/>
+        <n v="32100"/>
+        <n v="72000"/>
+        <n v="31400"/>
+        <n v="26100"/>
+        <n v="48600"/>
+        <n v="30050"/>
+        <n v="47440"/>
+        <n v="29000"/>
+        <n v="47360"/>
+        <n v="85000"/>
+        <n v="67300"/>
+        <n v="32200"/>
+        <n v="68000"/>
+        <n v="38600"/>
+        <n v="78800"/>
+        <n v="38500"/>
+        <n v="52000"/>
+        <n v="27800"/>
+        <n v="36800"/>
+        <n v="82000"/>
+        <n v="31500"/>
+        <n v="34900"/>
+        <n v="29100"/>
+        <n v="40500"/>
+        <n v="32700"/>
+        <n v="26800"/>
+        <n v="48200"/>
+        <n v="31900"/>
+        <n v="29800"/>
+        <n v="38000"/>
+        <n v="54200"/>
+        <n v="30200"/>
+        <n v="26900"/>
+        <n v="49800"/>
+        <n v="66500"/>
+        <n v="28200"/>
+        <n v="36100"/>
+        <n v="27500"/>
+        <n v="32400"/>
+        <n v="32000"/>
+        <n v="39200"/>
+        <n v="62000"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="performance_rating" numFmtId="0">
       <sharedItems/>
@@ -848,7 +900,7 @@
     <x v="0"/>
     <s v="F"/>
     <x v="0"/>
-    <n v="28500"/>
+    <x v="0"/>
     <s v="Excellent"/>
   </r>
   <r>
@@ -860,7 +912,7 @@
     <x v="0"/>
     <s v="M"/>
     <x v="1"/>
-    <n v="65000"/>
+    <x v="1"/>
     <s v="Excellent"/>
   </r>
   <r>
@@ -872,7 +924,7 @@
     <x v="1"/>
     <s v="F"/>
     <x v="2"/>
-    <n v="26300"/>
+    <x v="2"/>
     <s v="Good"/>
   </r>
   <r>
@@ -884,7 +936,7 @@
     <x v="2"/>
     <s v="M"/>
     <x v="3"/>
-    <n v="38200"/>
+    <x v="3"/>
     <s v="Excellent"/>
   </r>
   <r>
@@ -896,7 +948,7 @@
     <x v="0"/>
     <s v="F"/>
     <x v="4"/>
-    <n v="27750"/>
+    <x v="4"/>
     <s v="Average"/>
   </r>
   <r>
@@ -908,7 +960,7 @@
     <x v="1"/>
     <s v="M"/>
     <x v="5"/>
-    <n v="39760"/>
+    <x v="5"/>
     <s v="Good"/>
   </r>
   <r>
@@ -920,7 +972,7 @@
     <x v="0"/>
     <s v="F"/>
     <x v="6"/>
-    <n v="27000"/>
+    <x v="6"/>
     <s v="Good"/>
   </r>
   <r>
@@ -932,7 +984,7 @@
     <x v="2"/>
     <s v="M"/>
     <x v="7"/>
-    <n v="32100"/>
+    <x v="7"/>
     <s v="Excellent"/>
   </r>
   <r>
@@ -944,7 +996,7 @@
     <x v="0"/>
     <s v="F"/>
     <x v="8"/>
-    <n v="72000"/>
+    <x v="8"/>
     <s v="Excellent"/>
   </r>
   <r>
@@ -956,7 +1008,7 @@
     <x v="1"/>
     <s v="M"/>
     <x v="9"/>
-    <n v="31400"/>
+    <x v="9"/>
     <s v="Good"/>
   </r>
   <r>
@@ -968,7 +1020,7 @@
     <x v="0"/>
     <s v="F"/>
     <x v="10"/>
-    <n v="26100"/>
+    <x v="10"/>
     <s v="Average"/>
   </r>
   <r>
@@ -980,7 +1032,7 @@
     <x v="0"/>
     <s v="M"/>
     <x v="11"/>
-    <n v="48600"/>
+    <x v="11"/>
     <s v="Excellent"/>
   </r>
   <r>
@@ -992,7 +1044,7 @@
     <x v="1"/>
     <s v="F"/>
     <x v="12"/>
-    <n v="30050"/>
+    <x v="12"/>
     <s v="Good"/>
   </r>
   <r>
@@ -1004,7 +1056,7 @@
     <x v="0"/>
     <s v="M"/>
     <x v="13"/>
-    <n v="47440"/>
+    <x v="13"/>
     <s v="Excellent"/>
   </r>
   <r>
@@ -1016,7 +1068,7 @@
     <x v="0"/>
     <s v="F"/>
     <x v="14"/>
-    <n v="29000"/>
+    <x v="14"/>
     <s v="Good"/>
   </r>
   <r>
@@ -1028,7 +1080,7 @@
     <x v="1"/>
     <s v="M"/>
     <x v="15"/>
-    <n v="47360"/>
+    <x v="15"/>
     <s v="Excellent"/>
   </r>
   <r>
@@ -1040,7 +1092,7 @@
     <x v="2"/>
     <s v="F"/>
     <x v="16"/>
-    <n v="85000"/>
+    <x v="16"/>
     <s v="Excellent"/>
   </r>
   <r>
@@ -1052,7 +1104,7 @@
     <x v="0"/>
     <s v="M"/>
     <x v="17"/>
-    <n v="67300"/>
+    <x v="17"/>
     <s v="Excellent"/>
   </r>
   <r>
@@ -1064,7 +1116,7 @@
     <x v="3"/>
     <s v="F"/>
     <x v="18"/>
-    <n v="32200"/>
+    <x v="18"/>
     <s v="Good"/>
   </r>
   <r>
@@ -1076,7 +1128,7 @@
     <x v="0"/>
     <s v="M"/>
     <x v="19"/>
-    <n v="68000"/>
+    <x v="19"/>
     <s v="Excellent"/>
   </r>
   <r>
@@ -1088,7 +1140,7 @@
     <x v="0"/>
     <s v="F"/>
     <x v="20"/>
-    <n v="38600"/>
+    <x v="20"/>
     <s v="Good"/>
   </r>
   <r>
@@ -1100,7 +1152,7 @@
     <x v="1"/>
     <s v="M"/>
     <x v="21"/>
-    <n v="28500"/>
+    <x v="0"/>
     <s v="Average"/>
   </r>
   <r>
@@ -1112,7 +1164,7 @@
     <x v="2"/>
     <s v="F"/>
     <x v="22"/>
-    <n v="78800"/>
+    <x v="21"/>
     <s v="Excellent"/>
   </r>
   <r>
@@ -1124,7 +1176,7 @@
     <x v="0"/>
     <s v="M"/>
     <x v="23"/>
-    <n v="38500"/>
+    <x v="22"/>
     <s v="Good"/>
   </r>
   <r>
@@ -1136,7 +1188,7 @@
     <x v="0"/>
     <s v="F"/>
     <x v="24"/>
-    <n v="52000"/>
+    <x v="23"/>
     <s v="Excellent"/>
   </r>
   <r>
@@ -1148,7 +1200,7 @@
     <x v="1"/>
     <s v="M"/>
     <x v="25"/>
-    <n v="27800"/>
+    <x v="24"/>
     <s v="Average"/>
   </r>
   <r>
@@ -1160,7 +1212,7 @@
     <x v="0"/>
     <s v="F"/>
     <x v="26"/>
-    <n v="36800"/>
+    <x v="25"/>
     <s v="Good"/>
   </r>
   <r>
@@ -1172,7 +1224,7 @@
     <x v="0"/>
     <s v="M"/>
     <x v="27"/>
-    <n v="82000"/>
+    <x v="26"/>
     <s v="Excellent"/>
   </r>
   <r>
@@ -1184,7 +1236,7 @@
     <x v="1"/>
     <s v="F"/>
     <x v="28"/>
-    <n v="31500"/>
+    <x v="27"/>
     <s v="Good"/>
   </r>
   <r>
@@ -1196,7 +1248,7 @@
     <x v="2"/>
     <s v="M"/>
     <x v="29"/>
-    <n v="34900"/>
+    <x v="28"/>
     <s v="Good"/>
   </r>
   <r>
@@ -1208,7 +1260,7 @@
     <x v="0"/>
     <s v="F"/>
     <x v="30"/>
-    <n v="29100"/>
+    <x v="29"/>
     <s v="Good"/>
   </r>
   <r>
@@ -1220,7 +1272,7 @@
     <x v="1"/>
     <s v="M"/>
     <x v="31"/>
-    <n v="40500"/>
+    <x v="30"/>
     <s v="Excellent"/>
   </r>
   <r>
@@ -1232,7 +1284,7 @@
     <x v="2"/>
     <s v="F"/>
     <x v="32"/>
-    <n v="32700"/>
+    <x v="31"/>
     <s v="Good"/>
   </r>
   <r>
@@ -1244,7 +1296,7 @@
     <x v="0"/>
     <s v="M"/>
     <x v="33"/>
-    <n v="26800"/>
+    <x v="32"/>
     <s v="Average"/>
   </r>
   <r>
@@ -1256,7 +1308,7 @@
     <x v="0"/>
     <s v="F"/>
     <x v="34"/>
-    <n v="48200"/>
+    <x v="33"/>
     <s v="Excellent"/>
   </r>
   <r>
@@ -1268,7 +1320,7 @@
     <x v="1"/>
     <s v="M"/>
     <x v="35"/>
-    <n v="31900"/>
+    <x v="34"/>
     <s v="Good"/>
   </r>
   <r>
@@ -1280,7 +1332,7 @@
     <x v="0"/>
     <s v="F"/>
     <x v="36"/>
-    <n v="29800"/>
+    <x v="35"/>
     <s v="Average"/>
   </r>
   <r>
@@ -1292,7 +1344,7 @@
     <x v="0"/>
     <s v="M"/>
     <x v="37"/>
-    <n v="38000"/>
+    <x v="36"/>
     <s v="Good"/>
   </r>
   <r>
@@ -1304,7 +1356,7 @@
     <x v="1"/>
     <s v="F"/>
     <x v="38"/>
-    <n v="54200"/>
+    <x v="37"/>
     <s v="Excellent"/>
   </r>
   <r>
@@ -1316,7 +1368,7 @@
     <x v="0"/>
     <s v="M"/>
     <x v="39"/>
-    <n v="30200"/>
+    <x v="38"/>
     <s v="Average"/>
   </r>
   <r>
@@ -1328,7 +1380,7 @@
     <x v="2"/>
     <s v="F"/>
     <x v="40"/>
-    <n v="26900"/>
+    <x v="39"/>
     <s v="Good"/>
   </r>
   <r>
@@ -1340,7 +1392,7 @@
     <x v="0"/>
     <s v="M"/>
     <x v="41"/>
-    <n v="49800"/>
+    <x v="40"/>
     <s v="Excellent"/>
   </r>
   <r>
@@ -1352,7 +1404,7 @@
     <x v="0"/>
     <s v="F"/>
     <x v="42"/>
-    <n v="66500"/>
+    <x v="41"/>
     <s v="Excellent"/>
   </r>
   <r>
@@ -1364,7 +1416,7 @@
     <x v="1"/>
     <s v="M"/>
     <x v="43"/>
-    <n v="28200"/>
+    <x v="42"/>
     <s v="Average"/>
   </r>
   <r>
@@ -1376,7 +1428,7 @@
     <x v="0"/>
     <s v="F"/>
     <x v="44"/>
-    <n v="36100"/>
+    <x v="43"/>
     <s v="Good"/>
   </r>
   <r>
@@ -1388,7 +1440,7 @@
     <x v="0"/>
     <s v="M"/>
     <x v="45"/>
-    <n v="27500"/>
+    <x v="44"/>
     <s v="Average"/>
   </r>
   <r>
@@ -1400,7 +1452,7 @@
     <x v="1"/>
     <s v="F"/>
     <x v="46"/>
-    <n v="32400"/>
+    <x v="45"/>
     <s v="Good"/>
   </r>
   <r>
@@ -1412,7 +1464,7 @@
     <x v="2"/>
     <s v="M"/>
     <x v="47"/>
-    <n v="32000"/>
+    <x v="46"/>
     <s v="Good"/>
   </r>
   <r>
@@ -1424,7 +1476,7 @@
     <x v="0"/>
     <s v="F"/>
     <x v="48"/>
-    <n v="39200"/>
+    <x v="47"/>
     <s v="Excellent"/>
   </r>
   <r>
@@ -1436,14 +1488,14 @@
     <x v="1"/>
     <s v="M"/>
     <x v="49"/>
-    <n v="62000"/>
+    <x v="48"/>
     <s v="Excellent"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BCC9327F-8322-4FB7-AEAC-1FD0F4506841}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Department">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BCC9327F-8322-4FB7-AEAC-1FD0F4506841}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Department">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField dataField="1" showAll="0"/>
@@ -1578,7 +1630,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{56618293-34C7-4515-AA5C-F7293C7A4431}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{56618293-34C7-4515-AA5C-F7293C7A4431}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -1718,7 +1770,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9C1C0CC0-FCEA-47BC-8F08-A624975F8DBD}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Position">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9C1C0CC0-FCEA-47BC-8F08-A624975F8DBD}" name="PivotTable6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Position">
   <location ref="A3:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -1918,7 +1970,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AF1FD506-03CB-449E-9FB3-183E8BDBA681}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AF1FD506-03CB-449E-9FB3-183E8BDBA681}" name="PivotTable8" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:F10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField dataField="1" showAll="0"/>
@@ -2078,7 +2130,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FA9FA665-D739-40F1-A9DF-BE5939254722}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Hire_Date">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FA9FA665-D739-40F1-A9DF-BE5939254722}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Hire_Date">
   <location ref="A3:B13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField dataField="1" showAll="0"/>
@@ -2216,7 +2268,242 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{78C0B0A7-5DD6-4971-87AA-F03036A206C0}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Date_Hire">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{665C3739-027F-479D-8818-BA534B058A18}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:F10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="20">
+        <item x="12"/>
+        <item x="5"/>
+        <item x="14"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="9"/>
+        <item x="13"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="11"/>
+        <item x="18"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="15"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="51">
+        <item x="27"/>
+        <item x="16"/>
+        <item x="22"/>
+        <item x="49"/>
+        <item x="8"/>
+        <item x="19"/>
+        <item x="38"/>
+        <item x="1"/>
+        <item x="41"/>
+        <item x="17"/>
+        <item x="24"/>
+        <item x="31"/>
+        <item x="42"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="26"/>
+        <item x="5"/>
+        <item x="34"/>
+        <item x="48"/>
+        <item x="20"/>
+        <item x="15"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="44"/>
+        <item x="29"/>
+        <item x="37"/>
+        <item x="30"/>
+        <item x="46"/>
+        <item x="2"/>
+        <item x="23"/>
+        <item x="35"/>
+        <item x="4"/>
+        <item x="18"/>
+        <item x="9"/>
+        <item x="47"/>
+        <item x="32"/>
+        <item x="28"/>
+        <item x="40"/>
+        <item x="21"/>
+        <item x="39"/>
+        <item x="43"/>
+        <item x="10"/>
+        <item x="33"/>
+        <item x="25"/>
+        <item x="6"/>
+        <item x="36"/>
+        <item x="12"/>
+        <item x="14"/>
+        <item x="45"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0">
+      <items count="50">
+        <item x="10"/>
+        <item x="2"/>
+        <item x="32"/>
+        <item x="39"/>
+        <item x="6"/>
+        <item x="44"/>
+        <item x="4"/>
+        <item x="24"/>
+        <item x="42"/>
+        <item x="0"/>
+        <item x="14"/>
+        <item x="29"/>
+        <item x="35"/>
+        <item x="12"/>
+        <item x="38"/>
+        <item x="9"/>
+        <item x="27"/>
+        <item x="34"/>
+        <item x="46"/>
+        <item x="7"/>
+        <item x="18"/>
+        <item x="45"/>
+        <item x="31"/>
+        <item x="28"/>
+        <item x="43"/>
+        <item x="25"/>
+        <item x="36"/>
+        <item x="3"/>
+        <item x="22"/>
+        <item x="20"/>
+        <item x="47"/>
+        <item x="5"/>
+        <item x="30"/>
+        <item x="15"/>
+        <item x="13"/>
+        <item x="33"/>
+        <item x="11"/>
+        <item x="40"/>
+        <item x="23"/>
+        <item x="37"/>
+        <item x="48"/>
+        <item x="1"/>
+        <item x="41"/>
+        <item x="17"/>
+        <item x="19"/>
+        <item x="8"/>
+        <item x="21"/>
+        <item x="26"/>
+        <item x="16"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="0">
+      <items count="11">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="5"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of salary" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{78C0B0A7-5DD6-4971-87AA-F03036A206C0}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Date_Hire">
   <location ref="A9:B69" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField dataField="1" showAll="0"/>
@@ -2790,23 +3077,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64440D95-22DE-4BA5-8A63-8CAF5B277E5A}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="14"/>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="B1" s="12"/>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>125</v>
       </c>
@@ -2814,7 +3101,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>76</v>
       </c>
@@ -2822,7 +3109,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>89</v>
       </c>
@@ -2830,7 +3117,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>53</v>
       </c>
@@ -2838,7 +3125,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>38</v>
       </c>
@@ -2846,7 +3133,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>12</v>
       </c>
@@ -2854,7 +3141,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>128</v>
       </c>
@@ -2862,34 +3149,34 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="17" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-    </row>
-    <row r="14" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A14" s="19" t="s">
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+    </row>
+    <row r="14" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2904,23 +3191,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F26125FE-92FA-4CA7-81BA-EDE177B9BF43}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="1"/>
     <col min="2" max="2" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="14"/>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="B1" s="12"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="16"/>
       <c r="B2" s="16"/>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>127</v>
       </c>
@@ -2928,7 +3215,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>14</v>
       </c>
@@ -2936,7 +3223,7 @@
         <v>1175790</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>23</v>
       </c>
@@ -2944,7 +3231,7 @@
         <v>511870</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>28</v>
       </c>
@@ -2952,7 +3239,7 @@
         <v>360600</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>71</v>
       </c>
@@ -2960,7 +3247,7 @@
         <v>32200</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>128</v>
       </c>
@@ -2968,44 +3255,44 @@
         <v>2080460</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="18" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="19" t="s">
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3020,23 +3307,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{644AB5FA-4519-4986-ACB5-EE95A28B06E3}">
   <dimension ref="A1:C37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" customWidth="1"/>
     <col min="2" max="2" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="B1" s="14"/>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="B1" s="12"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="16"/>
       <c r="B2" s="16"/>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>145</v>
       </c>
@@ -3044,7 +3331,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>64</v>
       </c>
@@ -3052,7 +3339,7 @@
         <v>85000</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>92</v>
       </c>
@@ -3060,7 +3347,7 @@
         <v>82000</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>82</v>
       </c>
@@ -3068,7 +3355,7 @@
         <v>78800</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>42</v>
       </c>
@@ -3076,7 +3363,7 @@
         <v>72000</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>67</v>
       </c>
@@ -3084,7 +3371,7 @@
         <v>67266.666666666672</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>19</v>
       </c>
@@ -3092,7 +3379,7 @@
         <v>63500</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>85</v>
       </c>
@@ -3100,7 +3387,7 @@
         <v>53100</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>50</v>
       </c>
@@ -3108,7 +3395,7 @@
         <v>49200</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>57</v>
       </c>
@@ -3116,7 +3403,7 @@
         <v>47666.666666666664</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>27</v>
       </c>
@@ -3124,7 +3411,7 @@
         <v>39486.666666666664</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>77</v>
       </c>
@@ -3132,7 +3419,7 @@
         <v>38575</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>90</v>
       </c>
@@ -3140,7 +3427,7 @@
         <v>35933.333333333336</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>39</v>
       </c>
@@ -3148,7 +3435,7 @@
         <v>32150</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>70</v>
       </c>
@@ -3156,7 +3443,7 @@
         <v>32033.333333333332</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>94</v>
       </c>
@@ -3164,7 +3451,7 @@
         <v>30850</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>54</v>
       </c>
@@ -3172,7 +3459,7 @@
         <v>29616.666666666668</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>79</v>
       </c>
@@ -3180,7 +3467,7 @@
         <v>28166.666666666668</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>13</v>
       </c>
@@ -3188,7 +3475,7 @@
         <v>27578.571428571428</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>47</v>
       </c>
@@ -3196,7 +3483,7 @@
         <v>26450</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>128</v>
       </c>
@@ -3204,69 +3491,69 @@
         <v>41609.199999999997</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="18" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-    </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1">
-      <c r="A29" s="18" t="s">
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+    </row>
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="18"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="18"/>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="18"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="18"/>
-      <c r="B37" s="18"/>
-      <c r="C37" s="18"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="17"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="17"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3281,7 +3568,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B015D08-D1A4-40D4-89DF-5A78E4CE8B38}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.140625" customWidth="1"/>
@@ -3291,25 +3578,25 @@
     <col min="6" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>126</v>
       </c>
@@ -3317,7 +3604,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>127</v>
       </c>
@@ -3337,7 +3624,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>76</v>
       </c>
@@ -3354,7 +3641,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>89</v>
       </c>
@@ -3371,7 +3658,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>53</v>
       </c>
@@ -3391,7 +3678,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>38</v>
       </c>
@@ -3408,7 +3695,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>12</v>
       </c>
@@ -3425,7 +3712,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>128</v>
       </c>
@@ -3445,51 +3732,51 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="18" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="18" t="s">
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3504,23 +3791,23 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F6719B7-7BAB-478F-BE03-DA8238DA54F4}">
   <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.140625" customWidth="1"/>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="12"/>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="B1" s="18"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>147</v>
       </c>
@@ -3528,7 +3815,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>130</v>
       </c>
@@ -3536,7 +3823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>131</v>
       </c>
@@ -3544,7 +3831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>132</v>
       </c>
@@ -3552,7 +3839,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>133</v>
       </c>
@@ -3560,7 +3847,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>134</v>
       </c>
@@ -3568,7 +3855,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>135</v>
       </c>
@@ -3576,7 +3863,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>136</v>
       </c>
@@ -3584,7 +3871,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>137</v>
       </c>
@@ -3592,7 +3879,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>138</v>
       </c>
@@ -3600,7 +3887,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>128</v>
       </c>
@@ -3608,59 +3895,59 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="18" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-    </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1">
-      <c r="A19" s="18" t="s">
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3673,9 +3960,169 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66E2F93C-AED1-4AFC-ADB9-F060D2AB1529}">
+  <dimension ref="A3:F10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" customWidth="1"/>
+    <col min="6" max="6" width="22.85546875" customWidth="1"/>
+    <col min="7" max="50" width="6" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20">
+        <v>138700</v>
+      </c>
+      <c r="D5" s="20">
+        <v>78800</v>
+      </c>
+      <c r="E5" s="20">
+        <v>206300</v>
+      </c>
+      <c r="F5" s="20">
+        <v>423800</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20">
+        <v>31500</v>
+      </c>
+      <c r="D6" s="20">
+        <v>34900</v>
+      </c>
+      <c r="E6" s="20">
+        <v>185100</v>
+      </c>
+      <c r="F6" s="20">
+        <v>251500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="20">
+        <v>32200</v>
+      </c>
+      <c r="C7" s="20">
+        <v>109310</v>
+      </c>
+      <c r="D7" s="20">
+        <v>117000</v>
+      </c>
+      <c r="E7" s="20">
+        <v>356240</v>
+      </c>
+      <c r="F7" s="20">
+        <v>614750</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20">
+        <v>63800</v>
+      </c>
+      <c r="D8" s="20">
+        <v>64800</v>
+      </c>
+      <c r="E8" s="20">
+        <v>223300</v>
+      </c>
+      <c r="F8" s="20">
+        <v>351900</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20">
+        <v>168560</v>
+      </c>
+      <c r="D9" s="20">
+        <v>65100</v>
+      </c>
+      <c r="E9" s="20">
+        <v>204850</v>
+      </c>
+      <c r="F9" s="20">
+        <v>438510</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" s="20">
+        <v>32200</v>
+      </c>
+      <c r="C10" s="20">
+        <v>511870</v>
+      </c>
+      <c r="D10" s="20">
+        <v>360600</v>
+      </c>
+      <c r="E10" s="20">
+        <v>1175790</v>
+      </c>
+      <c r="F10" s="20">
+        <v>2080460</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FD9D665-80CB-42DB-976A-7593D3D36622}">
   <dimension ref="A9:B69"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
@@ -3683,7 +4130,7 @@
     <col min="5" max="5" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>129</v>
       </c>
@@ -3691,7 +4138,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>130</v>
       </c>
@@ -3699,7 +4146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>42449</v>
       </c>
@@ -3707,7 +4154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>131</v>
       </c>
@@ -3715,7 +4162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>42830</v>
       </c>
@@ -3723,7 +4170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>132</v>
       </c>
@@ -3731,7 +4178,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>43132</v>
       </c>
@@ -3739,7 +4186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>43234</v>
       </c>
@@ -3747,7 +4194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>43266</v>
       </c>
@@ -3755,7 +4202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>43393</v>
       </c>
@@ -3763,7 +4210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>133</v>
       </c>
@@ -3771,7 +4218,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>43610</v>
       </c>
@@ -3779,7 +4226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <v>43699</v>
       </c>
@@ -3787,7 +4234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>43723</v>
       </c>
@@ -3795,7 +4242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <v>43800</v>
       </c>
@@ -3803,7 +4250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>134</v>
       </c>
@@ -3811,7 +4258,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>43891</v>
       </c>
@@ -3819,7 +4266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>43943</v>
       </c>
@@ -3827,7 +4274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>43990</v>
       </c>
@@ -3835,7 +4282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>44075</v>
       </c>
@@ -3843,7 +4290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
         <v>44140</v>
       </c>
@@ -3851,7 +4298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>135</v>
       </c>
@@ -3859,7 +4306,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
         <v>44280</v>
       </c>
@@ -3867,7 +4314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <v>44392</v>
       </c>
@@ -3875,7 +4322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
         <v>44430</v>
       </c>
@@ -3883,7 +4330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <v>44510</v>
       </c>
@@ -3891,7 +4338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
         <v>44550</v>
       </c>
@@ -3899,7 +4346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>136</v>
       </c>
@@ -3907,7 +4354,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
         <v>44566</v>
       </c>
@@ -3915,7 +4362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
         <v>44571</v>
       </c>
@@ -3923,7 +4370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
         <v>44591</v>
       </c>
@@ -3931,7 +4378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
         <v>44635</v>
       </c>
@@ -3939,7 +4386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
         <v>44656</v>
       </c>
@@ -3947,7 +4394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
         <v>44693</v>
       </c>
@@ -3955,7 +4402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
         <v>44791</v>
       </c>
@@ -3963,7 +4410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
         <v>44842</v>
       </c>
@@ -3971,7 +4418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
         <v>44905</v>
       </c>
@@ -3979,7 +4426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
         <v>137</v>
       </c>
@@ -3987,7 +4434,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
         <v>44936</v>
       </c>
@@ -3995,7 +4442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
         <v>44972</v>
       </c>
@@ -4003,7 +4450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
         <v>44977</v>
       </c>
@@ -4011,7 +4458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
         <v>45034</v>
       </c>
@@ -4019,7 +4466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
         <v>45061</v>
       </c>
@@ -4027,7 +4474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
         <v>45087</v>
       </c>
@@ -4035,7 +4482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
         <v>45125</v>
       </c>
@@ -4043,7 +4490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
         <v>45153</v>
       </c>
@@ -4051,7 +4498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
         <v>45170</v>
       </c>
@@ -4059,7 +4506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
         <v>45260</v>
       </c>
@@ -4067,7 +4514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
         <v>138</v>
       </c>
@@ -4075,7 +4522,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
         <v>45303</v>
       </c>
@@ -4083,7 +4530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="11">
         <v>45313</v>
       </c>
@@ -4091,7 +4538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="11">
         <v>45334</v>
       </c>
@@ -4099,7 +4546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="11">
         <v>45336</v>
       </c>
@@ -4107,7 +4554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="11">
         <v>45352</v>
       </c>
@@ -4115,7 +4562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="11">
         <v>45392</v>
       </c>
@@ -4123,7 +4570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="11">
         <v>45413</v>
       </c>
@@ -4131,7 +4578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="11">
         <v>45448</v>
       </c>
@@ -4139,7 +4586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="11">
         <v>45493</v>
       </c>
@@ -4147,7 +4594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="11">
         <v>45505</v>
       </c>
@@ -4155,7 +4602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="11">
         <v>45536</v>
       </c>
@@ -4163,7 +4610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
         <v>128</v>
       </c>
@@ -4176,10 +4623,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J51"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
     <col min="2" max="3" width="13" customWidth="1"/>
@@ -4192,7 +4639,7 @@
     <col min="10" max="10" width="26.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4224,7 +4671,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -4256,7 +4703,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -4288,7 +4735,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -4320,7 +4767,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -4352,7 +4799,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -4384,7 +4831,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -4416,7 +4863,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -4448,7 +4895,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -4480,7 +4927,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -4512,7 +4959,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -4544,7 +4991,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -4576,7 +5023,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -4608,7 +5055,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -4640,7 +5087,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -4672,7 +5119,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -4704,7 +5151,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -4736,7 +5183,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -4768,7 +5215,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -4800,7 +5247,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -4832,7 +5279,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -4864,7 +5311,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -4896,7 +5343,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -4928,7 +5375,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -4960,7 +5407,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -4992,7 +5439,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -5024,7 +5471,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -5056,7 +5503,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -5088,7 +5535,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -5120,7 +5567,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -5152,7 +5599,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -5184,7 +5631,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -5216,7 +5663,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -5248,7 +5695,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -5280,7 +5727,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -5312,7 +5759,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -5344,7 +5791,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -5376,7 +5823,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -5408,7 +5855,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -5440,7 +5887,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -5472,7 +5919,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -5504,7 +5951,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -5536,7 +5983,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -5568,7 +6015,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -5600,7 +6047,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -5632,7 +6079,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -5664,7 +6111,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -5696,7 +6143,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -5728,7 +6175,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -5760,7 +6207,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -5792,7 +6239,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -5829,58 +6276,58 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18.75">
+    <row r="1" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>124</v>
       </c>
